--- a/data/data_gdp_final.xlsx
+++ b/data/data_gdp_final.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,192 +417,192 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>CountryID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="C1" t="n">
         <v>1970</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" t="n">
         <v>1971</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="E1" t="n">
         <v>1972</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="F1" t="n">
         <v>1973</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="G1" t="n">
         <v>1974</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="H1" t="n">
         <v>1975</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" t="n">
         <v>1976</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="J1" t="n">
         <v>1977</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="K1" t="n">
         <v>1978</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="L1" t="n">
         <v>1979</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="M1" t="n">
         <v>1980</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="N1" t="n">
         <v>1981</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="O1" t="n">
         <v>1982</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="P1" t="n">
         <v>1983</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="Q1" t="n">
         <v>1984</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="R1" t="n">
         <v>1985</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="S1" t="n">
         <v>1986</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="T1" t="n">
         <v>1987</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="U1" t="n">
         <v>1988</v>
       </c>
-      <c r="V1" s="1" t="n">
+      <c r="V1" t="n">
         <v>1989</v>
       </c>
-      <c r="W1" s="1" t="n">
+      <c r="W1" t="n">
         <v>1990</v>
       </c>
-      <c r="X1" s="1" t="n">
+      <c r="X1" t="n">
         <v>1991</v>
       </c>
-      <c r="Y1" s="1" t="n">
+      <c r="Y1" t="n">
         <v>1992</v>
       </c>
-      <c r="Z1" s="1" t="n">
+      <c r="Z1" t="n">
         <v>1993</v>
       </c>
-      <c r="AA1" s="1" t="n">
+      <c r="AA1" t="n">
         <v>1994</v>
       </c>
-      <c r="AB1" s="1" t="n">
+      <c r="AB1" t="n">
         <v>1995</v>
       </c>
-      <c r="AC1" s="1" t="n">
+      <c r="AC1" t="n">
         <v>1996</v>
       </c>
-      <c r="AD1" s="1" t="n">
+      <c r="AD1" t="n">
         <v>1997</v>
       </c>
-      <c r="AE1" s="1" t="n">
+      <c r="AE1" t="n">
         <v>1998</v>
       </c>
-      <c r="AF1" s="1" t="n">
+      <c r="AF1" t="n">
         <v>1999</v>
       </c>
-      <c r="AG1" s="1" t="n">
+      <c r="AG1" t="n">
         <v>2000</v>
       </c>
-      <c r="AH1" s="1" t="n">
+      <c r="AH1" t="n">
         <v>2001</v>
       </c>
-      <c r="AI1" s="1" t="n">
+      <c r="AI1" t="n">
         <v>2002</v>
       </c>
-      <c r="AJ1" s="1" t="n">
+      <c r="AJ1" t="n">
         <v>2003</v>
       </c>
-      <c r="AK1" s="1" t="n">
+      <c r="AK1" t="n">
         <v>2004</v>
       </c>
-      <c r="AL1" s="1" t="n">
+      <c r="AL1" t="n">
         <v>2005</v>
       </c>
-      <c r="AM1" s="1" t="n">
+      <c r="AM1" t="n">
         <v>2006</v>
       </c>
-      <c r="AN1" s="1" t="n">
+      <c r="AN1" t="n">
         <v>2007</v>
       </c>
-      <c r="AO1" s="1" t="n">
+      <c r="AO1" t="n">
         <v>2008</v>
       </c>
-      <c r="AP1" s="1" t="n">
+      <c r="AP1" t="n">
         <v>2009</v>
       </c>
-      <c r="AQ1" s="1" t="n">
+      <c r="AQ1" t="n">
         <v>2010</v>
       </c>
-      <c r="AR1" s="1" t="n">
+      <c r="AR1" t="n">
         <v>2011</v>
       </c>
-      <c r="AS1" s="1" t="n">
+      <c r="AS1" t="n">
         <v>2012</v>
       </c>
-      <c r="AT1" s="1" t="n">
+      <c r="AT1" t="n">
         <v>2013</v>
       </c>
-      <c r="AU1" s="1" t="n">
+      <c r="AU1" t="n">
         <v>2014</v>
       </c>
-      <c r="AV1" s="1" t="n">
+      <c r="AV1" t="n">
         <v>2015</v>
       </c>
-      <c r="AW1" s="1" t="n">
+      <c r="AW1" t="n">
         <v>2016</v>
       </c>
-      <c r="AX1" s="1" t="n">
+      <c r="AX1" t="n">
         <v>2017</v>
       </c>
-      <c r="AY1" s="1" t="n">
+      <c r="AY1" t="n">
         <v>2018</v>
       </c>
-      <c r="AZ1" s="1" t="n">
+      <c r="AZ1" t="n">
         <v>2019</v>
       </c>
-      <c r="BA1" s="1" t="n">
+      <c r="BA1" t="n">
         <v>2020</v>
       </c>
-      <c r="BB1" s="1" t="n">
+      <c r="BB1" t="n">
         <v>2021</v>
       </c>
-      <c r="BC1" s="1" t="n">
+      <c r="BC1" t="n">
         <v>2022</v>
       </c>
-      <c r="BD1" s="1" t="n">
+      <c r="BD1" t="n">
         <v>2023</v>
       </c>
-      <c r="BE1" s="1" t="n">
+      <c r="BE1" t="n">
         <v>2024</v>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>CAGR</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>GDP_Multiplier</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Growth_Volatility</t>
         </is>
